--- a/data/merged/2026-09-23/MERGED_JP_Stick-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_JP_Stick-Vacuum_2026-09-23.xlsx
@@ -7067,50 +7067,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7436,7 +7392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -17357,40 +17313,40 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B0GSPJ52BH</t>
+          <t>B0FY6JRNZB</t>
         </is>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>YIEEC</t>
+          <t>Waihipa</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/YIEECJAPAN%E5%85%AC%E5%BC%8F%E8%B2%A9%E5%A3%B2%E5%BA%97/page/B68F9D87-B40B-4E0D-8B4D-E895D5766148?lp_asin=B0GSPJ52BH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Waihipa</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>YIEEC 吸尘器 无线【强力吸力!史上最轻!第三代独立自走!业界首创AI灰尘自动检测!惊人静音 】无线棒式吸尘器s拥有业界顶级的轻量。 实现业界最高级别的静音性。 使用方便。 实现更短时间。 商用吸尘器 轻便、快速、不停。 单手即可轻松使用。</t>
+          <t>Waihipa 手持式吸尘器 有线【38000Pa超强吸力 1.1千克 超轻・静音设计 2026创新款】 Waihipa 棒式吸尘器s6M电源线 HEPA多重过滤 垃圾丢弃简单 旋风式 小巧 独居 家用 地毯/窗帘/沙发适用 PSE认证 附带日语</t>
         </is>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GSPJ52BH?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FY6JRNZB?psc=1</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71qHiXmaHYL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31scqQ1T3FL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>B0GSPJ52BH</t>
+          <t>B0FY6JRNZB</t>
         </is>
       </c>
       <c r="M44" s="12" t="inlineStr">
@@ -17404,13 +17360,13 @@
         </is>
       </c>
       <c r="O44" s="13">
-        <v>8577</v>
+        <v>8883</v>
       </c>
       <c r="P44" s="13">
-        <v>59280</v>
+        <v>4331</v>
       </c>
       <c r="Q44" s="14">
-        <v>0.87</v>
+        <v>0.33</v>
       </c>
       <c r="R44" s="15" t="inlineStr">
         <is>
@@ -17419,53 +17375,61 @@
       </c>
       <c r="S44" s="16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56</t>
         </is>
       </c>
       <c r="T44" s="13">
-        <v>61</v>
-      </c>
-      <c r="U44" s="14"/>
+        <v>233</v>
+      </c>
+      <c r="U44" s="14">
+        <v>0</v>
+      </c>
       <c r="V44" s="13">
-        <v>951539</v>
-      </c>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
+        <v>929437</v>
+      </c>
+      <c r="W44" s="13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X44" s="13">
+        <v>398900</v>
+      </c>
       <c r="Y44" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z44" s="13">
-        <v>15599</v>
+        <v>3989</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="13"/>
       <c r="AD44" s="17">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="AE44" s="13">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="AF44" s="18">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG44" s="19">
-        <v>0</v>
+        <v>0.0644</v>
       </c>
       <c r="AH44" s="13">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="AI44" s="14">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL44" s="17">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="AM44" s="11" t="inlineStr">
         <is>
@@ -17483,7 +17447,7 @@
       </c>
       <c r="AS44" s="12" t="inlineStr">
         <is>
-          <t>YIEEC公式通販</t>
+          <t>山田家電</t>
         </is>
       </c>
       <c r="AT44" s="11" t="inlineStr">
@@ -17498,12 +17462,12 @@
       </c>
       <c r="AV44" s="12" t="inlineStr">
         <is>
-          <t>深圳市 广东 518112 CN</t>
+          <t>宁波市 浙江省 315010 CN</t>
         </is>
       </c>
       <c r="AW44" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATLSOLL87JRMD</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2EJASQEDQ30BJ</t>
         </is>
       </c>
       <c r="AX44" s="11"/>
@@ -17520,11 +17484,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD44" s="11"/>
       <c r="BE44" s="11"/>
       <c r="BF44" s="11"/>
       <c r="BG44" s="11"/>
@@ -17536,38 +17496,38 @@
       </c>
       <c r="BJ44" s="20" t="inlineStr">
         <is>
-          <t>3.6 Kilograms</t>
+          <t>2.02 Kilograms</t>
         </is>
       </c>
       <c r="BK44" s="20" t="inlineStr">
         <is>
-          <t>3.60 kg</t>
+          <t>2.02 kg</t>
         </is>
       </c>
       <c r="BL44" s="20" t="inlineStr">
         <is>
-          <t>18長さ x 29幅 x 44高さ cm</t>
+          <t>15長さ x 8幅 x 18高さ cm</t>
         </is>
       </c>
       <c r="BM44" s="20"/>
       <c r="BN44" s="20" t="inlineStr">
         <is>
-          <t>3.6 kg</t>
+          <t>2.02 kg</t>
         </is>
       </c>
       <c r="BO44" s="20" t="inlineStr">
         <is>
-          <t>3.60 kg</t>
+          <t>2.02 kg</t>
         </is>
       </c>
       <c r="BP44" s="20" t="inlineStr">
         <is>
-          <t>44.3 x 31.9 x 19 cm</t>
+          <t>35 x 25.6 x 17.2 cm</t>
         </is>
       </c>
       <c r="BQ44" s="20" t="inlineStr">
         <is>
-          <t>44.30 x 31.90 x 19.00 cm</t>
+          <t>35.00 x 25.60 x 17.20 cm</t>
         </is>
       </c>
       <c r="BR44" s="11" t="inlineStr">
@@ -17583,40 +17543,40 @@
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>B0FY6JRNZB</t>
+          <t>B0FQ4WD1GZ</t>
         </is>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Waihipa</t>
+          <t>Emdou</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Waihipa</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Emdou</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Waihipa 手持式吸尘器 有线【38000Pa超强吸力 1.1千克 超轻・静音设计 2026创新款】 Waihipa 棒式吸尘器s6M电源线 HEPA多重过滤 垃圾丢弃简单 旋风式 小巧 独居 家用 地毯/窗帘/沙发适用 PSE认证 附带日语</t>
+          <t>【2025新改良型号】Emdou多功能吸尘器壁挂收纳支架V6 V7 V8 V10 V11 V12 V15 Digital SLIM等系列兼容壁挂式立式无线吸尘器收纳功能 (黑色)</t>
         </is>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FY6JRNZB?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FQ4WD1GZ?psc=1</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31scqQ1T3FL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51vO6Djc2cL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>B0FY6JRNZB</t>
+          <t>B0FQ4WD1GZ</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
@@ -17630,13 +17590,13 @@
         </is>
       </c>
       <c r="O45" s="13">
-        <v>8883</v>
+        <v>6218</v>
       </c>
       <c r="P45" s="13">
-        <v>4331</v>
+        <v>3668</v>
       </c>
       <c r="Q45" s="14">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="R45" s="15" t="inlineStr">
         <is>
@@ -17645,17 +17605,17 @@
       </c>
       <c r="S45" s="16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T45" s="13">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="U45" s="14">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="V45" s="13">
-        <v>929437</v>
+        <v>779544</v>
       </c>
       <c r="W45" s="13" t="inlineStr">
         <is>
@@ -17663,43 +17623,43 @@
         </is>
       </c>
       <c r="X45" s="13">
-        <v>398900</v>
+        <v>329583</v>
       </c>
       <c r="Y45" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z45" s="13">
-        <v>3989</v>
+        <v>3208</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="13"/>
       <c r="AD45" s="17">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AE45" s="13">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AF45" s="18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG45" s="19">
-        <v>0.0644</v>
+        <v>0.0123</v>
       </c>
       <c r="AH45" s="13">
         <v>472</v>
       </c>
       <c r="AI45" s="14">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="11" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AL45" s="17">
-        <v>287</v>
+        <v>364</v>
       </c>
       <c r="AM45" s="11" t="inlineStr">
         <is>
@@ -17717,7 +17677,7 @@
       </c>
       <c r="AS45" s="12" t="inlineStr">
         <is>
-          <t>山田家電</t>
+          <t>Emdou Direct JP</t>
         </is>
       </c>
       <c r="AT45" s="11" t="inlineStr">
@@ -17727,17 +17687,17 @@
       </c>
       <c r="AU45" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV45" s="12" t="inlineStr">
         <is>
-          <t>宁波市 浙江省 315010 CN</t>
+          <t>江戸川区 東京都 1330057 JP</t>
         </is>
       </c>
       <c r="AW45" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2EJASQEDQ30BJ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AY12P0DDZNKI2</t>
         </is>
       </c>
       <c r="AX45" s="11"/>
@@ -17766,38 +17726,42 @@
       </c>
       <c r="BJ45" s="20" t="inlineStr">
         <is>
-          <t>2.02 Kilograms</t>
+          <t>3.36 Kilograms</t>
         </is>
       </c>
       <c r="BK45" s="20" t="inlineStr">
         <is>
-          <t>2.02 kg</t>
+          <t>3.36 kg</t>
         </is>
       </c>
       <c r="BL45" s="20" t="inlineStr">
         <is>
-          <t>15長さ x 8幅 x 18高さ cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="20"/>
+          <t>29 x 23 x 127 cm</t>
+        </is>
+      </c>
+      <c r="BM45" s="20" t="inlineStr">
+        <is>
+          <t>29.00 x 23.00 x 127.00 cm</t>
+        </is>
+      </c>
       <c r="BN45" s="20" t="inlineStr">
         <is>
-          <t>2.02 kg</t>
+          <t>3.36 kg</t>
         </is>
       </c>
       <c r="BO45" s="20" t="inlineStr">
         <is>
-          <t>2.02 kg</t>
+          <t>3.36 kg</t>
         </is>
       </c>
       <c r="BP45" s="20" t="inlineStr">
         <is>
-          <t>35 x 25.6 x 17.2 cm</t>
+          <t>44.4 x 23.9 x 11 cm</t>
         </is>
       </c>
       <c r="BQ45" s="20" t="inlineStr">
         <is>
-          <t>35.00 x 25.60 x 17.20 cm</t>
+          <t>44.40 x 23.90 x 11.00 cm</t>
         </is>
       </c>
       <c r="BR45" s="11" t="inlineStr">
@@ -17813,40 +17777,40 @@
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>B0FQ4WD1GZ</t>
+          <t>B0HJ7DG8LF</t>
         </is>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Emdou</t>
+          <t>Migdla</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Emdou</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Migdla</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>【2025新改良型号】Emdou多功能吸尘器壁挂收纳支架V6 V7 V8 V10 V11 V12 V15 Digital SLIM等系列兼容壁挂式立式无线吸尘器收纳功能 (黑色)</t>
+          <t>无线吸尘器 [45000Pa超强吸力,约950克轻便] 手持吸尘器 两用 HEPA过滤器 Type-C充电式 车用</t>
         </is>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FQ4WD1GZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HJ7DG8LF?psc=1</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51vO6Djc2cL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51N+eEHXlkL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>B0FQ4WD1GZ</t>
+          <t>B0HJ7DG8LF</t>
         </is>
       </c>
       <c r="M46" s="12" t="inlineStr">
@@ -17860,13 +17824,13 @@
         </is>
       </c>
       <c r="O46" s="13">
-        <v>6218</v>
+        <v>3223</v>
       </c>
       <c r="P46" s="13">
-        <v>3668</v>
+        <v>19384</v>
       </c>
       <c r="Q46" s="14">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
       <c r="R46" s="15" t="inlineStr">
         <is>
@@ -17875,61 +17839,53 @@
       </c>
       <c r="S46" s="16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T46" s="13">
-        <v>243</v>
-      </c>
-      <c r="U46" s="14">
-        <v>-0.57</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="U46" s="14"/>
       <c r="V46" s="13">
-        <v>779544</v>
-      </c>
-      <c r="W46" s="13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X46" s="13">
-        <v>329583</v>
-      </c>
+        <v>518567</v>
+      </c>
+      <c r="W46" s="13"/>
+      <c r="X46" s="13"/>
       <c r="Y46" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="13">
-        <v>3208</v>
+        <v>3899</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="13"/>
       <c r="AD46" s="17">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="AE46" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF46" s="18">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG46" s="19">
-        <v>0.0123</v>
+        <v>0.015</v>
       </c>
       <c r="AH46" s="13">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="AI46" s="14">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="11" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AL46" s="17">
-        <v>364</v>
+        <v>12</v>
       </c>
       <c r="AM46" s="11" t="inlineStr">
         <is>
@@ -17943,11 +17899,11 @@
         <v>10</v>
       </c>
       <c r="AR46" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS46" s="12" t="inlineStr">
         <is>
-          <t>Emdou Direct JP</t>
+          <t>zifengfushi</t>
         </is>
       </c>
       <c r="AT46" s="11" t="inlineStr">
@@ -17957,17 +17913,17 @@
       </c>
       <c r="AU46" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV46" s="12" t="inlineStr">
         <is>
-          <t>江戸川区 東京都 1330057 JP</t>
+          <t>桂林市 广西 541000 CN</t>
         </is>
       </c>
       <c r="AW46" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AY12P0DDZNKI2</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2D9RYBYH64NYI</t>
         </is>
       </c>
       <c r="AX46" s="11"/>
@@ -17984,7 +17940,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="11"/>
+      <c r="BD46" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE46" s="11"/>
       <c r="BF46" s="11"/>
       <c r="BG46" s="11"/>
@@ -17996,42 +17956,38 @@
       </c>
       <c r="BJ46" s="20" t="inlineStr">
         <is>
-          <t>3.36 Kilograms</t>
+          <t>760 g</t>
         </is>
       </c>
       <c r="BK46" s="20" t="inlineStr">
         <is>
-          <t>3.36 kg</t>
+          <t>760.00 g</t>
         </is>
       </c>
       <c r="BL46" s="20" t="inlineStr">
         <is>
-          <t>29 x 23 x 127 cm</t>
-        </is>
-      </c>
-      <c r="BM46" s="20" t="inlineStr">
-        <is>
-          <t>29.00 x 23.00 x 127.00 cm</t>
-        </is>
-      </c>
+          <t>33長さ x 9幅 x 16.5高さ cm</t>
+        </is>
+      </c>
+      <c r="BM46" s="20"/>
       <c r="BN46" s="20" t="inlineStr">
         <is>
-          <t>3.36 kg</t>
+          <t>760 g</t>
         </is>
       </c>
       <c r="BO46" s="20" t="inlineStr">
         <is>
-          <t>3.36 kg</t>
+          <t>760.00 g</t>
         </is>
       </c>
       <c r="BP46" s="20" t="inlineStr">
         <is>
-          <t>44.4 x 23.9 x 11 cm</t>
+          <t>33.6 x 16.7 x 9.1 cm</t>
         </is>
       </c>
       <c r="BQ46" s="20" t="inlineStr">
         <is>
-          <t>44.40 x 23.90 x 11.00 cm</t>
+          <t>33.60 x 16.70 x 9.10 cm</t>
         </is>
       </c>
       <c r="BR46" s="11" t="inlineStr">
@@ -18047,40 +18003,40 @@
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>B0HJ7DG8LF</t>
+          <t>B0HHDR6C15</t>
         </is>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="12"/>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Migdla</t>
+          <t>Fochai</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Migdla</t>
+          <t>https://www.amazon.co.jp/stores/Fochai/page/DE5D837A-02A0-4080-858C-7DDD6DC2652B?lp_asin=B0HHDR6C15&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>无线吸尘器 [45000Pa超强吸力,约950克轻便] 手持吸尘器 两用 HEPA过滤器 Type-C充电式 车用</t>
+          <t>吸尘器 无线 强力吸45000Pa 35分钟运行 超轻 静音 棒型 独居 适用于宠物的毛发・猫砂 主体0.5千克 充电式小巧s适合独自生活、宠物毛发、猫砂。 2WAY规格,只需取下延长管即可使用。 适用于车内、楼梯、地板、地毯。 Type-C充电</t>
         </is>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HJ7DG8LF?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HHDR6C15?psc=1</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51N+eEHXlkL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61znGEgO5vL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>B0HJ7DG8LF</t>
+          <t>B0HHDR6C15</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
@@ -18094,13 +18050,13 @@
         </is>
       </c>
       <c r="O47" s="13">
-        <v>3223</v>
+        <v>9873</v>
       </c>
       <c r="P47" s="13">
-        <v>19384</v>
+        <v>16004</v>
       </c>
       <c r="Q47" s="14">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="R47" s="15" t="inlineStr">
         <is>
@@ -18109,15 +18065,15 @@
       </c>
       <c r="S47" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>63</t>
         </is>
       </c>
       <c r="T47" s="13">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="U47" s="14"/>
       <c r="V47" s="13">
-        <v>518567</v>
+        <v>362964</v>
       </c>
       <c r="W47" s="13"/>
       <c r="X47" s="13"/>
@@ -18125,28 +18081,28 @@
         <v>1</v>
       </c>
       <c r="Z47" s="13">
-        <v>3899</v>
+        <v>6258</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="13"/>
       <c r="AD47" s="17">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="AE47" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF47" s="18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AG47" s="19">
-        <v>0.015</v>
+        <v>0.0862</v>
       </c>
       <c r="AH47" s="13">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="AI47" s="14">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="11" t="inlineStr">
@@ -18166,14 +18122,14 @@
       <c r="AO47" s="11"/>
       <c r="AP47"/>
       <c r="AQ47" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR47" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS47" s="12" t="inlineStr">
         <is>
-          <t>zifengfushi</t>
+          <t>Fochai JP公式店--HKXW</t>
         </is>
       </c>
       <c r="AT47" s="11" t="inlineStr">
@@ -18183,17 +18139,17 @@
       </c>
       <c r="AU47" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV47" s="12" t="inlineStr">
         <is>
-          <t>桂林市 广西 541000 CN</t>
+          <t>Kwun Tong Hong Kong 999077 HK</t>
         </is>
       </c>
       <c r="AW47" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2D9RYBYH64NYI</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3F58EHMKQMLN4</t>
         </is>
       </c>
       <c r="AX47" s="11"/>
@@ -18210,11 +18166,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD47" s="11"/>
       <c r="BE47" s="11"/>
       <c r="BF47" s="11"/>
       <c r="BG47" s="11"/>
@@ -18226,38 +18178,38 @@
       </c>
       <c r="BJ47" s="20" t="inlineStr">
         <is>
-          <t>760 g</t>
+          <t>1.58 Kilograms</t>
         </is>
       </c>
       <c r="BK47" s="20" t="inlineStr">
         <is>
-          <t>760.00 g</t>
+          <t>1.58 kg</t>
         </is>
       </c>
       <c r="BL47" s="20" t="inlineStr">
         <is>
-          <t>33長さ x 9幅 x 16.5高さ cm</t>
+          <t>23長さ x 8幅 x 13高さ cm</t>
         </is>
       </c>
       <c r="BM47" s="20"/>
       <c r="BN47" s="20" t="inlineStr">
         <is>
-          <t>760 g</t>
+          <t>1.58 kg</t>
         </is>
       </c>
       <c r="BO47" s="20" t="inlineStr">
         <is>
-          <t>760.00 g</t>
+          <t>1.58 kg</t>
         </is>
       </c>
       <c r="BP47" s="20" t="inlineStr">
         <is>
-          <t>33.6 x 16.7 x 9.1 cm</t>
+          <t>36.3 x 20.5 x 15.7 cm</t>
         </is>
       </c>
       <c r="BQ47" s="20" t="inlineStr">
         <is>
-          <t>33.60 x 16.70 x 9.10 cm</t>
+          <t>36.30 x 20.50 x 15.70 cm</t>
         </is>
       </c>
       <c r="BR47" s="11" t="inlineStr">
@@ -18273,40 +18225,40 @@
       <c r="B48" s="11"/>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>B0HHDR6C15</t>
+          <t>B0GZMHZNK9</t>
         </is>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Fochai</t>
+          <t>LUNINO</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Fochai/page/DE5D837A-02A0-4080-858C-7DDD6DC2652B?lp_asin=B0HHDR6C15&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%9B%E3%83%BC%E3%83%A0%E3%83%9A%E3%83%BC%E3%82%B8/page/049DBEB4-0B31-4E22-8DCE-D709B73B139D?lp_asin=B0GZMHZNK9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>吸尘器 无线 强力吸45000Pa 35分钟运行 超轻 静音 棒型 独居 适用于宠物的毛发・猫砂 主体0.5千克 充电式小巧s适合独自生活、宠物毛发、猫砂。 2WAY规格,只需取下延长管即可使用。 适用于车内、楼梯、地板、地毯。 Type-C充电</t>
+          <t>吸尘器 无线【10月前发售】45000KPa强力吸力!惊人的静音!超轻!AI控制!绿色LED!新一代LED液晶!自走式!自立式】sCOSPA 排名第一 LUNINO 无绳吸尘器 棒状吸尘器 Cyclone 大容量电池长时间运行 1.5L 防尘杯防</t>
         </is>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHDR6C15?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GZMHZNK9?psc=1</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61znGEgO5vL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/617cYujAmsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>B0HHDR6C15</t>
+          <t>B0GZMHZNK9</t>
         </is>
       </c>
       <c r="M48" s="12" t="inlineStr">
@@ -18320,13 +18272,13 @@
         </is>
       </c>
       <c r="O48" s="13">
-        <v>9873</v>
+        <v>3937</v>
       </c>
       <c r="P48" s="13">
-        <v>16004</v>
+        <v>111875</v>
       </c>
       <c r="Q48" s="14">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="R48" s="15" t="inlineStr">
         <is>
@@ -18335,15 +18287,15 @@
       </c>
       <c r="S48" s="16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T48" s="13">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="U48" s="14"/>
       <c r="V48" s="13">
-        <v>362964</v>
+        <v>356966</v>
       </c>
       <c r="W48" s="13"/>
       <c r="X48" s="13"/>
@@ -18351,37 +18303,37 @@
         <v>1</v>
       </c>
       <c r="Z48" s="13">
-        <v>6258</v>
+        <v>10499</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="13"/>
       <c r="AD48" s="17">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AE48" s="13">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="18">
         <v>5</v>
       </c>
-      <c r="AF48" s="18">
-        <v>4.7</v>
-      </c>
       <c r="AG48" s="19">
-        <v>0.0862</v>
+        <v>0.1176</v>
       </c>
       <c r="AH48" s="13">
-        <v>472</v>
+        <v>532</v>
       </c>
       <c r="AI48" s="14">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AL48" s="17">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AM48" s="11" t="inlineStr">
         <is>
@@ -18392,14 +18344,14 @@
       <c r="AO48" s="11"/>
       <c r="AP48"/>
       <c r="AQ48" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR48" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS48" s="12" t="inlineStr">
         <is>
-          <t>Fochai JP公式店--HKXW</t>
+          <t>Sunhom</t>
         </is>
       </c>
       <c r="AT48" s="11" t="inlineStr">
@@ -18409,17 +18361,17 @@
       </c>
       <c r="AU48" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV48" s="12" t="inlineStr">
         <is>
-          <t>Kwun Tong Hong Kong 999077 HK</t>
+          <t>东莞市 广东省 523076 CN</t>
         </is>
       </c>
       <c r="AW48" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3F58EHMKQMLN4</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZFYZU5D0P11T</t>
         </is>
       </c>
       <c r="AX48" s="11"/>
@@ -18448,38 +18400,38 @@
       </c>
       <c r="BJ48" s="20" t="inlineStr">
         <is>
-          <t>1.58 Kilograms</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="BK48" s="20" t="inlineStr">
         <is>
-          <t>1.58 kg</t>
+          <t>1,000.00 g</t>
         </is>
       </c>
       <c r="BL48" s="20" t="inlineStr">
         <is>
-          <t>23長さ x 8幅 x 13高さ cm</t>
+          <t>15長さ x 15幅 x 15高さ cm</t>
         </is>
       </c>
       <c r="BM48" s="20"/>
       <c r="BN48" s="20" t="inlineStr">
         <is>
-          <t>1.58 kg</t>
+          <t>3.22 kg</t>
         </is>
       </c>
       <c r="BO48" s="20" t="inlineStr">
         <is>
-          <t>1.58 kg</t>
+          <t>3.22 kg</t>
         </is>
       </c>
       <c r="BP48" s="20" t="inlineStr">
         <is>
-          <t>36.3 x 20.5 x 15.7 cm</t>
+          <t>40.3 x 27.9 x 18.4 cm</t>
         </is>
       </c>
       <c r="BQ48" s="20" t="inlineStr">
         <is>
-          <t>36.30 x 20.50 x 15.70 cm</t>
+          <t>40.30 x 27.90 x 18.40 cm</t>
         </is>
       </c>
       <c r="BR48" s="11" t="inlineStr">
@@ -18495,155 +18447,135 @@
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>B0GZMHZNK9</t>
+          <t>B0CP7M3WQN</t>
         </is>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="12"/>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>LUNINO</t>
+          <t>東芝(TOSHIBA)</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%9B%E3%83%BC%E3%83%A0%E3%83%9A%E3%83%BC%E3%82%B8/page/049DBEB4-0B31-4E22-8DCE-D709B73B139D?lp_asin=B0GZMHZNK9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E6%9D%B1%E8%8A%9D%EF%BC%88TOSHIBA%EF%BC%89/page/9E65C0C7-C424-4127-8D4B-399C1795153A?lp_asin=B0CP7M3WQN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>吸尘器 无线【10月前发售】45000KPa强力吸力!惊人的静音!超轻!AI控制!绿色LED!新一代LED液晶!自走式!自立式】sCOSPA 排名第一 LUNINO 无绳吸尘器 棒状吸尘器 Cyclone 大容量电池长时间运行 1.5L 防尘杯防</t>
+          <t>东芝(TOSHIBA) 棒式吸尘器 无绳 单身生活 轻量 易于清洁Torneo VC-CLW32 Hs顺滑的自走式/无脱落刷/拨动灯/可拆卸式电池/垃圾处理简单</t>
         </is>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GZMHZNK9?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CP7M3WQN?psc=1</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/617cYujAmsL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41gQRWipmGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>B0GZMHZNK9</t>
+          <t>B0CP7M3WQN</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:スティッククリーナー</t>
-        </is>
-      </c>
-      <c r="N49" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O49" s="13">
-        <v>3937</v>
-      </c>
-      <c r="P49" s="13">
-        <v>111875</v>
-      </c>
-      <c r="Q49" s="14">
-        <v>0.92</v>
-      </c>
+          <t>ホーム＆キッチン:家電:消耗品・アクセサリ:生活家電消耗品・アクセサリ:掃除機用部品・アクセサリ:掃除機用紙パック</t>
+        </is>
+      </c>
+      <c r="N49" s="12"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="14"/>
       <c r="R49" s="15" t="inlineStr">
         <is>
-          <t>スティッククリーナー</t>
+          <t>掃除機用紙パック</t>
         </is>
       </c>
       <c r="S49" s="16" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="T49" s="13">
-        <v>34</v>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="T49" s="13"/>
       <c r="U49" s="14"/>
-      <c r="V49" s="13">
-        <v>356966</v>
-      </c>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
+      <c r="V49" s="13"/>
+      <c r="W49" s="13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X49" s="13">
+        <v>2606100</v>
+      </c>
       <c r="Y49" s="17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z49" s="13">
-        <v>10499</v>
+        <v>165</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="13"/>
       <c r="AD49" s="17">
+        <v>338</v>
+      </c>
+      <c r="AE49" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="18">
         <v>4</v>
       </c>
-      <c r="AE49" s="13">
-        <v>4</v>
-      </c>
-      <c r="AF49" s="18">
-        <v>5</v>
-      </c>
       <c r="AG49" s="19">
-        <v>0.1176</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="13">
-        <v>532</v>
+        <v>781</v>
       </c>
       <c r="AI49" s="14">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AL49" s="17">
-        <v>27</v>
+        <v>517</v>
       </c>
       <c r="AM49" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN49" s="11"/>
       <c r="AO49" s="11"/>
       <c r="AP49"/>
       <c r="AQ49" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR49" s="17">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="AS49" s="12" t="inlineStr">
         <is>
-          <t>Sunhom</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT49" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU49" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV49" s="12" t="inlineStr">
-        <is>
-          <t>东莞市 广东省 523076 CN</t>
-        </is>
-      </c>
-      <c r="AW49" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZFYZU5D0P11T</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU49" s="11"/>
+      <c r="AV49" s="12"/>
+      <c r="AW49" s="11"/>
       <c r="AX49" s="11"/>
       <c r="AY49" s="11" t="inlineStr">
         <is>
@@ -18658,7 +18590,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="11"/>
+      <c r="BD49" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE49" s="11"/>
       <c r="BF49" s="11"/>
       <c r="BG49" s="11"/>
@@ -18670,7 +18606,7 @@
       </c>
       <c r="BJ49" s="20" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>1 Kilograms</t>
         </is>
       </c>
       <c r="BK49" s="20" t="inlineStr">
@@ -18680,33 +18616,33 @@
       </c>
       <c r="BL49" s="20" t="inlineStr">
         <is>
-          <t>15長さ x 15幅 x 15高さ cm</t>
+          <t>15長さ x 23幅 x 99.3高さ cm</t>
         </is>
       </c>
       <c r="BM49" s="20"/>
       <c r="BN49" s="20" t="inlineStr">
         <is>
-          <t>3.22 kg</t>
+          <t>3.84 kg</t>
         </is>
       </c>
       <c r="BO49" s="20" t="inlineStr">
         <is>
-          <t>3.22 kg</t>
+          <t>3.84 kg</t>
         </is>
       </c>
       <c r="BP49" s="20" t="inlineStr">
         <is>
-          <t>40.3 x 27.9 x 18.4 cm</t>
+          <t>56.4 x 28.8 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ49" s="20" t="inlineStr">
         <is>
-          <t>40.30 x 27.90 x 18.40 cm</t>
+          <t>56.40 x 28.80 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR49" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -18717,310 +18653,104 @@
       <c r="B50" s="11"/>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>B0CP7M3WQN</t>
+          <t>B0FL6PSHWT</t>
         </is>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="12"/>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>東芝(TOSHIBA)</t>
-        </is>
-      </c>
+      <c r="F50" s="12"/>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E6%9D%B1%E8%8A%9D%EF%BC%88TOSHIBA%EF%BC%89/page/9E65C0C7-C424-4127-8D4B-399C1795153A?lp_asin=B0CP7M3WQN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>东芝(TOSHIBA) 棒式吸尘器 无绳 单身生活 轻量 易于清洁Torneo VC-CLW32 Hs顺滑的自走式/无脱落刷/拨动灯/可拆卸式电池/垃圾处理简单</t>
+          <t>吸尘器 纸袋式 日立 PKV-BK50P-C 米色 棒式 清洁器 无绳式 轻包棒 突出功率</t>
         </is>
       </c>
       <c r="I50" s="12"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CP7M3WQN?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FL6PSHWT?psc=1</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41gQRWipmGL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41PF6qX1tIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
-          <t>B0CP7M3WQN</t>
-        </is>
-      </c>
-      <c r="M50" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:消耗品・アクセサリ:生活家電消耗品・アクセサリ:掃除機用部品・アクセサリ:掃除機用紙パック</t>
-        </is>
-      </c>
+          <t>B0FL6PSHWT</t>
+        </is>
+      </c>
+      <c r="M50" s="12"/>
       <c r="N50" s="12"/>
       <c r="O50" s="13"/>
       <c r="P50" s="13"/>
       <c r="Q50" s="14"/>
-      <c r="R50" s="15" t="inlineStr">
-        <is>
-          <t>掃除機用紙パック</t>
-        </is>
-      </c>
-      <c r="S50" s="16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="R50" s="15"/>
+      <c r="S50" s="16"/>
       <c r="T50" s="13"/>
       <c r="U50" s="14"/>
       <c r="V50" s="13"/>
-      <c r="W50" s="13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X50" s="13">
-        <v>2606100</v>
-      </c>
-      <c r="Y50" s="17">
-        <v>6</v>
-      </c>
-      <c r="Z50" s="13">
-        <v>165</v>
-      </c>
+      <c r="W50" s="13"/>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="17"/>
+      <c r="Z50" s="13"/>
       <c r="AA50"/>
       <c r="AB50"/>
       <c r="AC50" s="13"/>
       <c r="AD50" s="17">
-        <v>338</v>
-      </c>
-      <c r="AE50" s="13">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AE50" s="13"/>
       <c r="AF50" s="18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG50" s="19">
         <v>0</v>
       </c>
-      <c r="AH50" s="13">
-        <v>781</v>
-      </c>
+      <c r="AH50" s="13"/>
       <c r="AI50" s="14">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="AJ50"/>
-      <c r="AK50" s="11" t="inlineStr">
-        <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AL50" s="17">
-        <v>517</v>
-      </c>
-      <c r="AM50" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK50" s="11"/>
+      <c r="AL50" s="17"/>
+      <c r="AM50" s="11"/>
       <c r="AN50" s="11"/>
       <c r="AO50" s="11"/>
       <c r="AP50"/>
-      <c r="AQ50" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="17">
-        <v>31</v>
-      </c>
-      <c r="AS50" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT50" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AQ50" s="17"/>
+      <c r="AR50" s="17"/>
+      <c r="AS50" s="12"/>
+      <c r="AT50" s="11"/>
       <c r="AU50" s="11"/>
       <c r="AV50" s="12"/>
       <c r="AW50" s="11"/>
       <c r="AX50" s="11"/>
-      <c r="AY50" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY50" s="11"/>
       <c r="AZ50" s="11"/>
       <c r="BA50" s="11"/>
       <c r="BB50" s="11"/>
-      <c r="BC50" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC50" s="11"/>
+      <c r="BD50" s="11"/>
       <c r="BE50" s="11"/>
       <c r="BF50" s="11"/>
       <c r="BG50" s="11"/>
       <c r="BH50" s="12"/>
-      <c r="BI50" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
-      <c r="BJ50" s="20" t="inlineStr">
-        <is>
-          <t>1 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK50" s="20" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BL50" s="20" t="inlineStr">
-        <is>
-          <t>15長さ x 23幅 x 99.3高さ cm</t>
-        </is>
-      </c>
+      <c r="BI50" s="20"/>
+      <c r="BJ50" s="20"/>
+      <c r="BK50" s="20"/>
+      <c r="BL50" s="20"/>
       <c r="BM50" s="20"/>
-      <c r="BN50" s="20" t="inlineStr">
-        <is>
-          <t>3.84 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="20" t="inlineStr">
-        <is>
-          <t>3.84 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="20" t="inlineStr">
-        <is>
-          <t>56.4 x 28.8 x 19.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="20" t="inlineStr">
-        <is>
-          <t>56.40 x 28.80 x 19.40 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0FL6PSHWT</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>吸尘器 纸袋式 日立 PKV-BK50P-C 米色 棒式 清洁器 无绳式 轻包棒 突出功率</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0FL6PSHWT?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41PF6qX1tIL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0FL6PSHWT</t>
-        </is>
-      </c>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="17">
-        <v>40</v>
-      </c>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51" s="11"/>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17"/>
-      <c r="AS51" s="12"/>
-      <c r="AT51" s="11"/>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51" s="11"/>
+      <c r="BN50" s="20"/>
+      <c r="BO50" s="20"/>
+      <c r="BP50" s="20"/>
+      <c r="BQ50" s="20"/>
+      <c r="BR50" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19349,67 +19079,59 @@
     <hyperlink ref="L43" r:id="rId321" tooltip="https://www.amazon.co.jp/dp/B002MZY69M"/>
     <hyperlink ref="M43" r:id="rId322" tooltip="https://www.amazon.co.jp/b?node=13698351"/>
     <hyperlink ref="N43" r:id="rId323"/>
-    <hyperlink ref="C44" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0GSPJ52BH"/>
-    <hyperlink ref="G44" r:id="rId325" tooltip="https://www.amazon.co.jp/stores/YIEECJAPAN%E5%85%AC%E5%BC%8F%E8%B2%A9%E5%A3%B2%E5%BA%97/page/B68F9D87-B40B-4E0D-8B4D-E895D5766148?lp_asin=B0GSPJ52BH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId326" tooltip="https://www.amazon.co.jp/dp/B0GSPJ52BH?psc=1"/>
-    <hyperlink ref="K44" r:id="rId327" tooltip="https://images-na.ssl-images-amazon.com/images/I/71qHiXmaHYL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B0GSPJ52BH"/>
+    <hyperlink ref="C44" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0FY6JRNZB"/>
+    <hyperlink ref="G44" r:id="rId325" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Waihipa"/>
+    <hyperlink ref="J44" r:id="rId326" tooltip="https://www.amazon.co.jp/dp/B0FY6JRNZB?psc=1"/>
+    <hyperlink ref="K44" r:id="rId327" tooltip="https://m.media-amazon.com/images/I/31scqQ1T3FL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B0FY6JRNZB"/>
     <hyperlink ref="M44" r:id="rId329" tooltip="https://www.amazon.co.jp/b?node=13698351"/>
     <hyperlink ref="N44" r:id="rId330"/>
-    <hyperlink ref="AW44" r:id="rId331" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATLSOLL87JRMD"/>
-    <hyperlink ref="C45" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B0FY6JRNZB"/>
-    <hyperlink ref="G45" r:id="rId333" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Waihipa"/>
-    <hyperlink ref="J45" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0FY6JRNZB?psc=1"/>
-    <hyperlink ref="K45" r:id="rId335" tooltip="https://m.media-amazon.com/images/I/31scqQ1T3FL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId336" tooltip="https://www.amazon.co.jp/dp/B0FY6JRNZB"/>
+    <hyperlink ref="AW44" r:id="rId331" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2EJASQEDQ30BJ"/>
+    <hyperlink ref="C45" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B0FQ4WD1GZ"/>
+    <hyperlink ref="G45" r:id="rId333" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Emdou"/>
+    <hyperlink ref="J45" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0FQ4WD1GZ?psc=1"/>
+    <hyperlink ref="K45" r:id="rId335" tooltip="https://images-na.ssl-images-amazon.com/images/I/51vO6Djc2cL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId336" tooltip="https://www.amazon.co.jp/dp/B0FQ4WD1GZ"/>
     <hyperlink ref="M45" r:id="rId337" tooltip="https://www.amazon.co.jp/b?node=13698351"/>
     <hyperlink ref="N45" r:id="rId338"/>
-    <hyperlink ref="AW45" r:id="rId339" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2EJASQEDQ30BJ"/>
-    <hyperlink ref="C46" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0FQ4WD1GZ"/>
-    <hyperlink ref="G46" r:id="rId341" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Emdou"/>
-    <hyperlink ref="J46" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B0FQ4WD1GZ?psc=1"/>
-    <hyperlink ref="K46" r:id="rId343" tooltip="https://images-na.ssl-images-amazon.com/images/I/51vO6Djc2cL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0FQ4WD1GZ"/>
+    <hyperlink ref="AW45" r:id="rId339" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AY12P0DDZNKI2"/>
+    <hyperlink ref="C46" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0HJ7DG8LF"/>
+    <hyperlink ref="G46" r:id="rId341" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Migdla"/>
+    <hyperlink ref="J46" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B0HJ7DG8LF?psc=1"/>
+    <hyperlink ref="K46" r:id="rId343" tooltip="https://images-na.ssl-images-amazon.com/images/I/51N+eEHXlkL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0HJ7DG8LF"/>
     <hyperlink ref="M46" r:id="rId345" tooltip="https://www.amazon.co.jp/b?node=13698351"/>
     <hyperlink ref="N46" r:id="rId346"/>
-    <hyperlink ref="AW46" r:id="rId347" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AY12P0DDZNKI2"/>
-    <hyperlink ref="C47" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0HJ7DG8LF"/>
-    <hyperlink ref="G47" r:id="rId349" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Migdla"/>
-    <hyperlink ref="J47" r:id="rId350" tooltip="https://www.amazon.co.jp/dp/B0HJ7DG8LF?psc=1"/>
-    <hyperlink ref="K47" r:id="rId351" tooltip="https://images-na.ssl-images-amazon.com/images/I/51N+eEHXlkL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId352" tooltip="https://www.amazon.co.jp/dp/B0HJ7DG8LF"/>
+    <hyperlink ref="AW46" r:id="rId347" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2D9RYBYH64NYI"/>
+    <hyperlink ref="C47" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0HHDR6C15"/>
+    <hyperlink ref="G47" r:id="rId349" tooltip="https://www.amazon.co.jp/stores/Fochai/page/DE5D837A-02A0-4080-858C-7DDD6DC2652B?lp_asin=B0HHDR6C15&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId350" tooltip="https://www.amazon.co.jp/dp/B0HHDR6C15?psc=1"/>
+    <hyperlink ref="K47" r:id="rId351" tooltip="https://images-na.ssl-images-amazon.com/images/I/61znGEgO5vL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId352" tooltip="https://www.amazon.co.jp/dp/B0HHDR6C15"/>
     <hyperlink ref="M47" r:id="rId353" tooltip="https://www.amazon.co.jp/b?node=13698351"/>
     <hyperlink ref="N47" r:id="rId354"/>
-    <hyperlink ref="AW47" r:id="rId355" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2D9RYBYH64NYI"/>
-    <hyperlink ref="C48" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B0HHDR6C15"/>
-    <hyperlink ref="G48" r:id="rId357" tooltip="https://www.amazon.co.jp/stores/Fochai/page/DE5D837A-02A0-4080-858C-7DDD6DC2652B?lp_asin=B0HHDR6C15&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId358" tooltip="https://www.amazon.co.jp/dp/B0HHDR6C15?psc=1"/>
-    <hyperlink ref="K48" r:id="rId359" tooltip="https://images-na.ssl-images-amazon.com/images/I/61znGEgO5vL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId360" tooltip="https://www.amazon.co.jp/dp/B0HHDR6C15"/>
+    <hyperlink ref="AW47" r:id="rId355" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3F58EHMKQMLN4"/>
+    <hyperlink ref="C48" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B0GZMHZNK9"/>
+    <hyperlink ref="G48" r:id="rId357" tooltip="https://www.amazon.co.jp/stores/%E3%83%9B%E3%83%BC%E3%83%A0%E3%83%9A%E3%83%BC%E3%82%B8/page/049DBEB4-0B31-4E22-8DCE-D709B73B139D?lp_asin=B0GZMHZNK9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId358" tooltip="https://www.amazon.co.jp/dp/B0GZMHZNK9?psc=1"/>
+    <hyperlink ref="K48" r:id="rId359" tooltip="https://images-na.ssl-images-amazon.com/images/I/617cYujAmsL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId360" tooltip="https://www.amazon.co.jp/dp/B0GZMHZNK9"/>
     <hyperlink ref="M48" r:id="rId361" tooltip="https://www.amazon.co.jp/b?node=13698351"/>
     <hyperlink ref="N48" r:id="rId362"/>
-    <hyperlink ref="AW48" r:id="rId363" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3F58EHMKQMLN4"/>
-    <hyperlink ref="C49" r:id="rId364" tooltip="https://www.amazon.co.jp/dp/B0GZMHZNK9"/>
-    <hyperlink ref="G49" r:id="rId365" tooltip="https://www.amazon.co.jp/stores/%E3%83%9B%E3%83%BC%E3%83%A0%E3%83%9A%E3%83%BC%E3%82%B8/page/049DBEB4-0B31-4E22-8DCE-D709B73B139D?lp_asin=B0GZMHZNK9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId366" tooltip="https://www.amazon.co.jp/dp/B0GZMHZNK9?psc=1"/>
-    <hyperlink ref="K49" r:id="rId367" tooltip="https://images-na.ssl-images-amazon.com/images/I/617cYujAmsL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId368" tooltip="https://www.amazon.co.jp/dp/B0GZMHZNK9"/>
-    <hyperlink ref="M49" r:id="rId369" tooltip="https://www.amazon.co.jp/b?node=13698351"/>
-    <hyperlink ref="N49" r:id="rId370"/>
-    <hyperlink ref="AW49" r:id="rId371" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZFYZU5D0P11T"/>
-    <hyperlink ref="C50" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B0CP7M3WQN"/>
-    <hyperlink ref="G50" r:id="rId373" tooltip="https://www.amazon.co.jp/stores/%E6%9D%B1%E8%8A%9D%EF%BC%88TOSHIBA%EF%BC%89/page/9E65C0C7-C424-4127-8D4B-399C1795153A?lp_asin=B0CP7M3WQN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId374" tooltip="https://www.amazon.co.jp/dp/B0CP7M3WQN?psc=1"/>
-    <hyperlink ref="K50" r:id="rId375" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41gQRWipmGL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId376" tooltip="https://www.amazon.co.jp/dp/B0CP7M3WQN"/>
-    <hyperlink ref="M50" r:id="rId377" tooltip="https://www.amazon.co.jp/b?node=13698391"/>
-    <hyperlink ref="C51" r:id="rId378" tooltip="https://www.amazon.co.jp/dp/B0FL6PSHWT"/>
-    <hyperlink ref="G51" r:id="rId379" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J51" r:id="rId380" tooltip="https://www.amazon.co.jp/dp/B0FL6PSHWT?psc=1"/>
-    <hyperlink ref="K51" r:id="rId381" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41PF6qX1tIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId382" tooltip="https://www.amazon.co.jp/dp/B0FL6PSHWT"/>
+    <hyperlink ref="AW48" r:id="rId363" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2ZFYZU5D0P11T"/>
+    <hyperlink ref="C49" r:id="rId364" tooltip="https://www.amazon.co.jp/dp/B0CP7M3WQN"/>
+    <hyperlink ref="G49" r:id="rId365" tooltip="https://www.amazon.co.jp/stores/%E6%9D%B1%E8%8A%9D%EF%BC%88TOSHIBA%EF%BC%89/page/9E65C0C7-C424-4127-8D4B-399C1795153A?lp_asin=B0CP7M3WQN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J49" r:id="rId366" tooltip="https://www.amazon.co.jp/dp/B0CP7M3WQN?psc=1"/>
+    <hyperlink ref="K49" r:id="rId367" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41gQRWipmGL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId368" tooltip="https://www.amazon.co.jp/dp/B0CP7M3WQN"/>
+    <hyperlink ref="M49" r:id="rId369" tooltip="https://www.amazon.co.jp/b?node=13698391"/>
+    <hyperlink ref="C50" r:id="rId370" tooltip="https://www.amazon.co.jp/dp/B0FL6PSHWT"/>
+    <hyperlink ref="G50" r:id="rId371" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J50" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B0FL6PSHWT?psc=1"/>
+    <hyperlink ref="K50" r:id="rId373" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41PF6qX1tIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId374" tooltip="https://www.amazon.co.jp/dp/B0FL6PSHWT"/>
   </hyperlinks>
-  <drawing r:id="rId383"/>
+  <drawing r:id="rId375"/>
 </worksheet>
 </file>
 
@@ -19479,7 +19201,7 @@
         <v>14301.843165014945</v>
       </c>
       <c r="G2" s="19">
-        <v>0.22352713655303363</v>
+        <v>0.22376711605477137</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19500,7 +19222,7 @@
         <v>29742.584988962473</v>
       </c>
       <c r="G3" s="19">
-        <v>0.09557130047996625</v>
+        <v>0.0956739061564997</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19521,7 +19243,7 @@
         <v>41115.451505016725</v>
       </c>
       <c r="G4" s="19">
-        <v>0.0578245046502224</v>
+        <v>0.05788658523707276</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19542,7 +19264,7 @@
         <v>29466.085726718888</v>
       </c>
       <c r="G5" s="19">
-        <v>0.040401554176409574</v>
+        <v>0.04044492942377416</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19563,7 +19285,7 @@
         <v>9989.137063227954</v>
       </c>
       <c r="G6" s="19">
-        <v>0.08453031874681341</v>
+        <v>0.08462107078742652</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19584,7 +19306,7 @@
         <v>12000.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.06248351764271524</v>
+        <v>0.06255060016192052</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19605,7 +19327,7 @@
         <v>18729.406554472986</v>
       </c>
       <c r="G8" s="19">
-        <v>0.03969830693225971</v>
+        <v>0.039740927170966944</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19615,18 +19337,18 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <v>2564</v>
+        <v>2503</v>
       </c>
       <c r="C9" s="13">
-        <v>21387036</v>
+        <v>20435497</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13">
-        <v>8341.277691107643</v>
+        <v>8164.401518178186</v>
       </c>
       <c r="G9" s="19">
-        <v>0.045078148350006154</v>
+        <v>0.0440529409694111</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19647,7 +19369,7 @@
         <v>12029.613189600508</v>
       </c>
       <c r="G10" s="19">
-        <v>0.02772552260060831</v>
+        <v>0.027755288816924215</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19668,7 +19390,7 @@
         <v>5980.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.05181174071274108</v>
+        <v>0.05186736597557112</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19689,7 +19411,7 @@
         <v>5680.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.05198755252377855</v>
+        <v>0.05204336653877292</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19710,7 +19432,7 @@
         <v>17380.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.015629670001230684</v>
+        <v>0.01564645006864022</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19731,7 +19453,7 @@
         <v>5632.706555671176</v>
       </c>
       <c r="G14" s="19">
-        <v>0.03379103008140087</v>
+        <v>0.03382730824738639</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19752,7 +19474,7 @@
         <v>5299.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.03377344890029712</v>
+        <v>0.03380970819106621</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19773,7 +19495,7 @@
         <v>8947.975719424461</v>
       </c>
       <c r="G16" s="19">
-        <v>0.019550273387366163</v>
+        <v>0.01957126262804041</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19794,7 +19516,7 @@
         <v>10980.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.015260465198052004</v>
+        <v>0.015276848885916435</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19815,7 +19537,7 @@
         <v>11381.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.01100581937094534</v>
+        <v>0.01101763525643282</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19836,7 +19558,7 @@
         <v>11998.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.009863042599201814</v>
+        <v>0.009873631595621105</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19857,7 +19579,7 @@
         <v>15199.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.0073489337013660574</v>
+        <v>0.007356823541835334</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19878,7 +19600,7 @@
         <v>5398.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.015787900631164403</v>
+        <v>0.01580485057552184</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19899,7 +19621,7 @@
         <v>7707.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.00982788023699432</v>
+        <v>0.009838431482980746</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19920,7 +19642,7 @@
         <v>13999.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.00453594472476661</v>
+        <v>0.004540814530606498</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19941,7 +19663,7 @@
         <v>5399.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.010531127481144183</v>
+        <v>0.010542433735787955</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19962,7 +19684,7 @@
         <v>4799.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.009722393150371843</v>
+        <v>0.009732831145059665</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19983,7 +19705,7 @@
         <v>3180.0</v>
       </c>
       <c r="G26" s="19">
-        <v>0.011427767717435257</v>
+        <v>0.011440036608117146</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20004,7 +19726,7 @@
         <v>3989.0</v>
       </c>
       <c r="G27" s="19">
-        <v>0.004096415197172946</v>
+        <v>0.004100813122601992</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20025,7 +19747,7 @@
         <v>3208.0</v>
       </c>
       <c r="G28" s="19">
-        <v>0.0042722270082104115</v>
+        <v>0.004276813685803795</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20046,7 +19768,7 @@
         <v>3899.0</v>
       </c>
       <c r="G29" s="19">
-        <v>0.0023382970867982912</v>
+        <v>0.00234080749058397</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20067,7 +19789,7 @@
         <v>10499.0</v>
       </c>
       <c r="G30" s="19">
-        <v>0.0005977601575273827</v>
+        <v>0.0005984019148861276</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20116,7 +19838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -20180,7 +19902,7 @@
         <v>19161.620191973292</v>
       </c>
       <c r="G2" s="19">
-        <v>0.5055292814571283</v>
+        <v>0.5060720194304622</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20201,7 +19923,7 @@
         <v>29399.0</v>
       </c>
       <c r="G3" s="19">
-        <v>0.030028657325199107</v>
+        <v>0.030060896194867823</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20222,7 +19944,7 @@
         <v>9989.137063227954</v>
       </c>
       <c r="G4" s="19">
-        <v>0.08453031874681341</v>
+        <v>0.08462107078742652</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20243,7 +19965,7 @@
         <v>18729.406554472986</v>
       </c>
       <c r="G5" s="19">
-        <v>0.03969830693225971</v>
+        <v>0.039740927170966944</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20264,7 +19986,7 @@
         <v>8164.401518178186</v>
       </c>
       <c r="G6" s="19">
-        <v>0.044005696302677616</v>
+        <v>0.0440529409694111</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20285,7 +20007,7 @@
         <v>12029.613189600508</v>
       </c>
       <c r="G7" s="19">
-        <v>0.02772552260060831</v>
+        <v>0.027755288816924215</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20306,7 +20028,7 @@
         <v>5680.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.05198755252377855</v>
+        <v>0.05204336653877292</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20327,7 +20049,7 @@
         <v>17380.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.015629670001230684</v>
+        <v>0.01564645006864022</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20348,7 +20070,7 @@
         <v>5299.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.03377344890029712</v>
+        <v>0.03380970819106621</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20369,7 +20091,7 @@
         <v>8947.975719424461</v>
       </c>
       <c r="G11" s="19">
-        <v>0.019550273387366163</v>
+        <v>0.01957126262804041</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20390,7 +20112,7 @@
         <v>29399.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.005889695669755094</v>
+        <v>0.005896018867260375</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20411,7 +20133,7 @@
         <v>10980.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.015260465198052004</v>
+        <v>0.015276848885916435</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20432,7 +20154,7 @@
         <v>11381.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.01100581937094534</v>
+        <v>0.01101763525643282</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20453,7 +20175,7 @@
         <v>11998.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.009863042599201814</v>
+        <v>0.009873631595621105</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20474,7 +20196,7 @@
         <v>15199.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.0073489337013660574</v>
+        <v>0.007356823541835334</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20495,7 +20217,7 @@
         <v>5110.979166666667</v>
       </c>
       <c r="G17" s="19">
-        <v>0.020253520631516024</v>
+        <v>0.020275264880847618</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20516,7 +20238,7 @@
         <v>5350.311808118081</v>
       </c>
       <c r="G18" s="19">
-        <v>0.01905800031646126</v>
+        <v>0.019078461051075364</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20537,7 +20259,7 @@
         <v>5998.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.014733029764939608</v>
+        <v>0.014748847196311029</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20558,7 +20280,7 @@
         <v>5398.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.015787900631164403</v>
+        <v>0.01580485057552184</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20579,7 +20301,7 @@
         <v>13999.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.00453594472476661</v>
+        <v>0.004540814530606498</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20600,130 +20322,109 @@
         <v>3180.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.011427767717435257</v>
+        <v>0.011440036608117146</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>YIEEC公式通販</t>
+          <t>山田家電</t>
         </is>
       </c>
       <c r="B23" s="13">
-        <v>61</v>
+        <v>233</v>
       </c>
       <c r="C23" s="13">
-        <v>951539</v>
+        <v>929437</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13">
-        <v>15599.0</v>
+        <v>3989.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.0010724520473285395</v>
+        <v>0.004100813122601992</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>山田家電</t>
+          <t>Emdou Direct JP</t>
         </is>
       </c>
       <c r="B24" s="13">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C24" s="13">
-        <v>929437</v>
+        <v>779544</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13">
-        <v>3989.0</v>
+        <v>3208.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.004096415197172946</v>
+        <v>0.004276813685803795</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Emdou Direct JP</t>
+          <t>zifengfushi</t>
         </is>
       </c>
       <c r="B25" s="13">
-        <v>243</v>
+        <v>133</v>
       </c>
       <c r="C25" s="13">
-        <v>779544</v>
+        <v>518567</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13">
-        <v>3208.0</v>
+        <v>3899.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.0042722270082104115</v>
+        <v>0.00234080749058397</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>zifengfushi</t>
+          <t>Sunhom</t>
         </is>
       </c>
       <c r="B26" s="13">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="C26" s="13">
-        <v>518567</v>
+        <v>356966</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13">
-        <v>3899.0</v>
+        <v>10499.0</v>
       </c>
       <c r="G26" s="19">
-        <v>0.0023382970867982912</v>
+        <v>0.0005984019148861276</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Sunhom</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B27" s="13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C27" s="13">
-        <v>356966</v>
+        <v>0</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="13">
-        <v>10499.0</v>
-      </c>
+      <c r="F27" s="13"/>
       <c r="G27" s="19">
-        <v>0.0005977601575273827</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <v>0</v>
-      </c>
-      <c r="C28" s="13">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="19">
         <v>0.0</v>
       </c>
     </row>
